--- a/AML.Core.Web.API/AML.Web/Files/Data-Customer Bulk upload Sample.xlsx
+++ b/AML.Core.Web.API/AML.Web/Files/Data-Customer Bulk upload Sample.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD1D86CB-6520-4967-98D4-93CCF468E6D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4813FC52-64D2-47D0-93C4-4C97463F45EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5292" yWindow="3396" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -21,10 +21,6 @@
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
-  <si>
-    <t xml:space="preserve">Customer ID (Mandatory field)
- </t>
-  </si>
   <si>
     <t>Date of Birth</t>
   </si>
@@ -82,6 +78,10 @@
   </si>
   <si>
     <t>Mode of Payment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Customer ID
+ </t>
   </si>
 </sst>
 </file>
@@ -516,43 +516,43 @@
   <sheetData>
     <row r="1" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="5" t="s">
+      <c r="E1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="8" t="s">
+      <c r="F1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="G1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="H1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="J1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="K1" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="L1" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="M1" s="9" t="s">
         <v>11</v>
-      </c>
-      <c r="M1" s="9" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
@@ -595,19 +595,12 @@
       <c r="A11" s="3"/>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C51" xr:uid="{E675A3D7-7CC7-4CBD-BF74-A88E5A379528}">
+      <formula1>#REF!</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{E675A3D7-7CC7-4CBD-BF74-A88E5A379528}">
-          <x14:formula1>
-            <xm:f>#REF!</xm:f>
-          </x14:formula1>
-          <xm:sqref>C2:C51</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
 </worksheet>
 </file>